--- a/tags.xlsx
+++ b/tags.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="70">
   <si>
     <t xml:space="preserve">Paper</t>
   </si>
@@ -109,12 +109,6 @@
     <t xml:space="preserve">BRC-VL</t>
   </si>
   <si>
-    <t xml:space="preserve">Rowhammer Cache A Last-Level Cache for Low-Overhead Rowhammer Tracking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rowhammer Cache</t>
-  </si>
-  <si>
     <t xml:space="preserve">Rubix Reducing the Overhead of Secure Rowhammer Mitigations via Randomized Line-to-Row Mapping</t>
   </si>
   <si>
@@ -233,6 +227,9 @@
   </si>
   <si>
     <t xml:space="preserve">Orange = Postponed</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -338,7 +335,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -367,6 +364,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -376,6 +377,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -562,7 +567,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N37"/>
+  <dimension ref="A1:N36"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17.88"/>
@@ -1014,7 +1019,7 @@
       <c r="B11" s="2" t="n">
         <v>2024</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="4" t="s">
         <v>30</v>
       </c>
       <c r="D11" s="5" t="n">
@@ -1037,29 +1042,27 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="I11" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="J11" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K11" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="I11" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J11" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5" t="b">
+        <v>1</v>
       </c>
       <c r="L11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>2024</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D12" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1085,41 +1088,39 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="J12" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="K12" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="J12" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5" t="b">
+        <v>1</v>
       </c>
       <c r="L12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C13" s="4" t="s">
+        <v>2025</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D13" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="F13" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="G13" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="D13" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
       <c r="H13" s="6" t="n">
         <f aca="false">FALSE()</f>
@@ -1129,25 +1130,25 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="J13" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="K13" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="J13" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
       <c r="L13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>2025</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D14" s="6" t="n">
         <f aca="false">FALSE()</f>
@@ -1185,7 +1186,7 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>2025</v>
@@ -1193,37 +1194,37 @@
       <c r="C15" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="E15" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
+      <c r="D15" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
       </c>
       <c r="F15" s="6" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="G15" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="H15" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="I15" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="G15" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
       <c r="J15" s="6" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="K15" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
+      <c r="K15" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
       </c>
       <c r="L15" s="2"/>
     </row>
@@ -1245,17 +1246,17 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="F16" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="F16" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
       <c r="G16" s="6" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="H16" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
+      <c r="H16" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
       </c>
       <c r="I16" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1389,17 +1390,17 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="I19" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
+      <c r="I19" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
       </c>
       <c r="J19" s="6" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="K19" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="K19" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
       <c r="L19" s="2"/>
     </row>
@@ -1413,13 +1414,13 @@
       <c r="C20" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D20" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="E20" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="D20" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
       <c r="F20" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1433,17 +1434,17 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="I20" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="I20" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
       <c r="J20" s="6" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="K20" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
+      <c r="K20" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
       </c>
       <c r="L20" s="2"/>
     </row>
@@ -1457,13 +1458,13 @@
       <c r="C21" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D21" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="E21" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
+      <c r="D21" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
       </c>
       <c r="F21" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1477,29 +1478,29 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="I21" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
+      <c r="I21" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
       </c>
       <c r="J21" s="6" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="K21" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="K21" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
       <c r="L21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>2025</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D22" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1525,19 +1526,19 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="J22" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K22" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
+      <c r="J22" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="K22" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
       </c>
       <c r="L22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>2025</v>
@@ -1565,13 +1566,13 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="I23" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J23" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
+      <c r="I23" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
       </c>
       <c r="K23" s="6" t="n">
         <f aca="false">FALSE()</f>
@@ -1609,17 +1610,17 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="I24" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
+      <c r="I24" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
       </c>
       <c r="J24" s="6" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="K24" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="K24" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
       <c r="L24" s="2"/>
     </row>
@@ -1653,29 +1654,29 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="I25" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="I25" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
       <c r="J25" s="6" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="K25" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
+      <c r="K25" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
       </c>
       <c r="L25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>2025</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D26" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1713,7 +1714,7 @@
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>2025</v>
@@ -1757,13 +1758,13 @@
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B28" s="2" t="n">
         <v>2025</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D28" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1801,13 +1802,13 @@
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B29" s="2" t="n">
         <v>2025</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D29" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1845,7 +1846,7 @@
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>2025</v>
@@ -1892,7 +1893,7 @@
         <v>63</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>64</v>
@@ -1961,13 +1962,13 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="I32" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="J32" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="I32" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J32" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
       <c r="K32" s="6" t="n">
         <f aca="false">FALSE()</f>
@@ -1976,112 +1977,70 @@
       <c r="L32" s="2"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2" t="s">
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8"/>
+      <c r="I33" s="8"/>
+      <c r="J33" s="8"/>
+      <c r="K33" s="8"/>
+      <c r="L33" s="8"/>
+      <c r="M33" s="8"/>
+      <c r="N33" s="8"/>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="8"/>
+      <c r="C34" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="B33" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C33" s="2" t="s">
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
+      <c r="I34" s="8"/>
+      <c r="J34" s="8"/>
+      <c r="K34" s="8"/>
+      <c r="L34" s="8"/>
+      <c r="M34" s="8"/>
+      <c r="N34" s="8"/>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="8"/>
+      <c r="C35" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="D33" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="E33" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="F33" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="G33" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="H33" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="I33" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J33" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="K33" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="L33" s="2"/>
-    </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="7"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
-      <c r="G34" s="7"/>
-      <c r="H34" s="7"/>
-      <c r="I34" s="7"/>
-      <c r="J34" s="7"/>
-      <c r="K34" s="7"/>
-      <c r="L34" s="7"/>
-      <c r="M34" s="7"/>
-      <c r="N34" s="7"/>
-    </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="7"/>
-      <c r="C35" s="8" t="s">
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="8"/>
+      <c r="I35" s="8"/>
+      <c r="J35" s="8"/>
+      <c r="K35" s="8"/>
+      <c r="L35" s="8"/>
+      <c r="M35" s="8"/>
+      <c r="N35" s="8"/>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="7"/>
-      <c r="G35" s="7"/>
-      <c r="H35" s="7"/>
-      <c r="I35" s="7"/>
-      <c r="J35" s="7"/>
-      <c r="K35" s="7"/>
-      <c r="L35" s="7"/>
-      <c r="M35" s="7"/>
-      <c r="N35" s="7"/>
-    </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="7"/>
-      <c r="C36" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D36" s="7"/>
-      <c r="E36" s="7"/>
-      <c r="F36" s="7"/>
-      <c r="G36" s="7"/>
-      <c r="H36" s="7"/>
-      <c r="I36" s="7"/>
-      <c r="J36" s="7"/>
-      <c r="K36" s="7"/>
-      <c r="L36" s="7"/>
-      <c r="M36" s="7"/>
-      <c r="N36" s="7"/>
-    </row>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="7"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
-      <c r="G37" s="7"/>
-      <c r="H37" s="7"/>
-      <c r="I37" s="7"/>
-      <c r="J37" s="7"/>
-      <c r="K37" s="7"/>
-      <c r="L37" s="7"/>
-      <c r="M37" s="7"/>
-      <c r="N37" s="7"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="8"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="8"/>
+      <c r="I36" s="8"/>
+      <c r="J36" s="8"/>
+      <c r="K36" s="8"/>
+      <c r="L36" s="8"/>
+      <c r="M36" s="8"/>
+      <c r="N36" s="8"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/tags.xlsx
+++ b/tags.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="72">
   <si>
     <t xml:space="preserve">Paper</t>
   </si>
@@ -94,6 +94,9 @@
     <t xml:space="preserve">Multi-Table Graphene</t>
   </si>
   <si>
+    <t xml:space="preserve">Incomplete</t>
+  </si>
+  <si>
     <t xml:space="preserve">PrIDE Achieving Secure Rowhammer Mitigation with Low-Cost In-DRAM Trackers</t>
   </si>
   <si>
@@ -131,6 +134,9 @@
   </si>
   <si>
     <t xml:space="preserve">Adaptive AI/ML Mitigation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Highly suspicious. Very vague</t>
   </si>
   <si>
     <t xml:space="preserve">CHaRM Checkpointed and Hashed Counters for Flexible and Efficient Rowhammer Mitigation</t>
@@ -269,7 +275,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -292,6 +298,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFF6F9D4"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC9211E"/>
+        <bgColor rgb="FF993366"/>
       </patternFill>
     </fill>
     <fill>
@@ -335,7 +347,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -364,7 +376,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -376,11 +388,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -447,7 +455,7 @@
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FFC9211E"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
@@ -843,7 +851,7 @@
       <c r="B7" s="2" t="n">
         <v>2024</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="7" t="s">
         <v>23</v>
       </c>
       <c r="D7" s="5" t="n">
@@ -878,17 +886,19 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="L7" s="2"/>
+      <c r="L7" s="2" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>2024</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D8" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -926,13 +936,13 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>2024</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D9" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -970,13 +980,13 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>2024</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>28</v>
+      <c r="C10" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="D10" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1014,13 +1024,13 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>2024</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D11" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1046,23 +1056,25 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="J11" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K11" s="5" t="b">
+      <c r="J11" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="L11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>2024</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D12" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1088,23 +1100,25 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="J12" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K12" s="5" t="b">
+      <c r="J12" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="L12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>2025</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D13" s="6" t="n">
         <f aca="false">FALSE()</f>
@@ -1142,13 +1156,13 @@
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>2025</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D14" s="6" t="n">
         <f aca="false">FALSE()</f>
@@ -1186,13 +1200,13 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>36</v>
+      <c r="C15" s="7" t="s">
+        <v>37</v>
       </c>
       <c r="D15" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1226,17 +1240,19 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="L15" s="2"/>
+      <c r="L15" s="2" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>38</v>
+      <c r="C16" s="4" t="s">
+        <v>40</v>
       </c>
       <c r="D16" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1274,13 +1290,13 @@
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>2025</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D17" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1318,13 +1334,13 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>2025</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D18" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1362,13 +1378,13 @@
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>2025</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D19" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1406,13 +1422,13 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>2025</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D20" s="6" t="n">
         <f aca="false">FALSE()</f>
@@ -1450,13 +1466,13 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>2025</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D21" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1494,13 +1510,13 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>2025</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D22" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1538,13 +1554,13 @@
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>2025</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D23" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1582,13 +1598,13 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>2025</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D24" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1626,13 +1642,13 @@
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>2025</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D25" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1670,13 +1686,13 @@
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>2025</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D26" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1714,13 +1730,13 @@
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>2025</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D27" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1758,13 +1774,13 @@
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B28" s="2" t="n">
         <v>2025</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D28" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1802,13 +1818,13 @@
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B29" s="2" t="n">
         <v>2025</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D29" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1846,13 +1862,13 @@
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>2025</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D30" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1890,13 +1906,13 @@
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>2026</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D31" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1934,13 +1950,13 @@
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>2026</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D32" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1994,7 +2010,7 @@
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="8"/>
       <c r="C34" s="9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D34" s="8"/>
       <c r="E34" s="8"/>
@@ -2011,7 +2027,7 @@
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="8"/>
       <c r="C35" s="10" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D35" s="8"/>
       <c r="E35" s="8"/>
@@ -2027,9 +2043,9 @@
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="C36" s="11"/>
+        <v>71</v>
+      </c>
+      <c r="C36" s="8"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
       <c r="F36" s="8"/>

--- a/tags.xlsx
+++ b/tags.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="74">
   <si>
     <t xml:space="preserve">Paper</t>
   </si>
@@ -55,6 +55,9 @@
     <t xml:space="preserve">Isolation_centric</t>
   </si>
   <si>
+    <t xml:space="preserve">Note</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alert Refresh System for Mitigating RowHammer</t>
   </si>
   <si>
@@ -157,6 +160,9 @@
     <t xml:space="preserve">One-Hot Counting (Counterpoint)</t>
   </si>
   <si>
+    <t xml:space="preserve">Not even published, details vague</t>
+  </si>
+  <si>
     <t xml:space="preserve">Investigating and Improving DRAM-Based Memory System Security by Analyzing and Exploiting DRAM Operations</t>
   </si>
   <si>
@@ -169,21 +175,24 @@
     <t xml:space="preserve">pTRR (pseudo-Target Row Refresh)</t>
   </si>
   <si>
+    <t xml:space="preserve">Attack vector analysis, irrelevant</t>
+  </si>
+  <si>
     <t xml:space="preserve">Not so Refreshing Attacking GPUs using RFM Rowhammer Mitigation</t>
   </si>
   <si>
     <t xml:space="preserve">Partitioning</t>
   </si>
   <si>
-    <t xml:space="preserve">Rubix</t>
-  </si>
-  <si>
     <t xml:space="preserve">PRACtical Subarray-Level Counter Update and Bank-Level Recovery Isolation for Efficient PRAC Rowhammer Mitigation</t>
   </si>
   <si>
     <t xml:space="preserve">PRACtical</t>
   </si>
   <si>
+    <t xml:space="preserve">Optimization to PRAC, nothing changed on the mitigation level</t>
+  </si>
+  <si>
     <t xml:space="preserve">Selective Subarray Isolation for Mitigating RowHammer Attack</t>
   </si>
   <si>
@@ -194,9 +203,6 @@
   </si>
   <si>
     <t xml:space="preserve">ABACuS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Self-Managing DRAM (SMD)</t>
   </si>
   <si>
     <t xml:space="preserve">Understanding and Mitigating Covert Channel and Side Channel Vulnerabilities Introduced by RowHammer</t>
@@ -575,15 +581,16 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N36"/>
+  <dimension ref="A1:N34"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="7.49"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="19.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="22.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="19.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="17.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="27.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="10.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="11.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="9.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="34.25"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -620,17 +627,19 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2"/>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -668,13 +677,13 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>2024</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -712,13 +721,13 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>2024</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D4" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -756,13 +765,13 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>2024</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D5" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -797,18 +806,18 @@
         <v>0</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>2024</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -846,13 +855,13 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>2024</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D7" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -887,18 +896,18 @@
         <v>0</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>2024</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D8" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -936,13 +945,13 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>2024</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D9" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -980,13 +989,13 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>2024</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D10" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1024,13 +1033,13 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>2024</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D11" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1068,13 +1077,13 @@
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>2024</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D12" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1112,13 +1121,13 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>2025</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D13" s="6" t="n">
         <f aca="false">FALSE()</f>
@@ -1156,13 +1165,13 @@
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>2025</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D14" s="6" t="n">
         <f aca="false">FALSE()</f>
@@ -1200,13 +1209,13 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>2025</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D15" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1241,18 +1250,18 @@
         <v>0</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>2025</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D16" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1290,13 +1299,13 @@
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>42</v>
+      <c r="C17" s="4" t="s">
+        <v>43</v>
       </c>
       <c r="D17" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1334,13 +1343,13 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>44</v>
+      <c r="C18" s="7" t="s">
+        <v>45</v>
       </c>
       <c r="D18" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1374,17 +1383,19 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="L18" s="2"/>
+      <c r="L18" s="2" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>2025</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D19" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1422,13 +1433,13 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>48</v>
+      <c r="C20" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="D20" s="6" t="n">
         <f aca="false">FALSE()</f>
@@ -1462,17 +1473,19 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="L20" s="2"/>
+      <c r="L20" s="2" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>2025</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D21" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1510,13 +1523,13 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>51</v>
+      <c r="C22" s="7" t="s">
+        <v>55</v>
       </c>
       <c r="D22" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1538,29 +1551,31 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="I22" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J22" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
+      <c r="I22" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
       </c>
       <c r="K22" s="6" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="L22" s="2"/>
+      <c r="L22" s="2" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>2025</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D23" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1582,29 +1597,29 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="I23" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
+      <c r="I23" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
       </c>
       <c r="J23" s="6" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="K23" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="K23" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
       <c r="L23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>55</v>
+      <c r="C24" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="D24" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1626,29 +1641,29 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="I24" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="I24" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
       <c r="J24" s="6" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="K24" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
+      <c r="K24" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
       </c>
       <c r="L24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>2025</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D25" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1686,13 +1701,13 @@
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>2025</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D26" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1730,13 +1745,13 @@
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>2025</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D27" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1774,13 +1789,13 @@
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B28" s="2" t="n">
         <v>2025</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="D28" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1818,13 +1833,13 @@
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D29" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1862,13 +1877,13 @@
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D30" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1890,13 +1905,13 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="I30" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="J30" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="I30" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
       <c r="K30" s="6" t="n">
         <f aca="false">FALSE()</f>
@@ -1905,96 +1920,42 @@
       <c r="L30" s="2"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B31" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D31" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="E31" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="F31" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="G31" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="H31" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="I31" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="J31" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K31" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="L31" s="2"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="8"/>
+      <c r="I31" s="8"/>
+      <c r="J31" s="8"/>
+      <c r="K31" s="8"/>
+      <c r="L31" s="8"/>
+      <c r="M31" s="8"/>
+      <c r="N31" s="8"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B32" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D32" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="E32" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="F32" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="G32" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="H32" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="I32" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J32" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="K32" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="L32" s="2"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D32" s="8"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="8"/>
+      <c r="I32" s="8"/>
+      <c r="J32" s="8"/>
+      <c r="K32" s="8"/>
+      <c r="L32" s="8"/>
+      <c r="M32" s="8"/>
+      <c r="N32" s="8"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="8"/>
-      <c r="C33" s="8"/>
+      <c r="C33" s="10" t="s">
+        <v>72</v>
+      </c>
       <c r="D33" s="8"/>
       <c r="E33" s="8"/>
       <c r="F33" s="8"/>
@@ -2008,10 +1969,10 @@
       <c r="N33" s="8"/>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="8"/>
-      <c r="C34" s="9" t="s">
-        <v>69</v>
-      </c>
+      <c r="B34" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="C34" s="8"/>
       <c r="D34" s="8"/>
       <c r="E34" s="8"/>
       <c r="F34" s="8"/>
@@ -2024,40 +1985,6 @@
       <c r="M34" s="8"/>
       <c r="N34" s="8"/>
     </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="8"/>
-      <c r="C35" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="8"/>
-      <c r="G35" s="8"/>
-      <c r="H35" s="8"/>
-      <c r="I35" s="8"/>
-      <c r="J35" s="8"/>
-      <c r="K35" s="8"/>
-      <c r="L35" s="8"/>
-      <c r="M35" s="8"/>
-      <c r="N35" s="8"/>
-    </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="8"/>
-      <c r="H36" s="8"/>
-      <c r="I36" s="8"/>
-      <c r="J36" s="8"/>
-      <c r="K36" s="8"/>
-      <c r="L36" s="8"/>
-      <c r="M36" s="8"/>
-      <c r="N36" s="8"/>
-    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/tags.xlsx
+++ b/tags.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="75">
   <si>
     <t xml:space="preserve">Paper</t>
   </si>
@@ -31,12 +31,6 @@
     <t xml:space="preserve">Mitigation</t>
   </si>
   <si>
-    <t xml:space="preserve">Long_term</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Short_term</t>
-  </si>
-  <si>
     <t xml:space="preserve">Hardware_based</t>
   </si>
   <si>
@@ -124,12 +118,15 @@
     <t xml:space="preserve">Rubix-D (Dynamic Randomization)</t>
   </si>
   <si>
-    <t xml:space="preserve">A Simulation-based Evaluation Framework for Inter-VM RowHammer Mitigation Techniques</t>
+    <t xml:space="preserve">Siloz: Leveraging DRAM Isolation Domains to Prevent Inter-VM Rowhammer</t>
   </si>
   <si>
     <t xml:space="preserve">Siloz</t>
   </si>
   <si>
+    <t xml:space="preserve">Preventing Rowhammer Exploits via Low-Cost Domain-Aware Memory Allocation</t>
+  </si>
+  <si>
     <t xml:space="preserve">Citadel</t>
   </si>
   <si>
@@ -217,6 +214,9 @@
     <t xml:space="preserve">Bank-Level PRAC</t>
   </si>
   <si>
+    <t xml:space="preserve">This is specifically against covert channel</t>
+  </si>
+  <si>
     <t xml:space="preserve">When Mitigations Backfire Timing Channel Attacks and Defense for PRAC-Based RowHammer Mitigations</t>
   </si>
   <si>
@@ -235,13 +235,16 @@
     <t xml:space="preserve">Optimized Row Access Prefetcher (ORAP)</t>
   </si>
   <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
     <t xml:space="preserve">Green = Reviewed</t>
   </si>
   <si>
     <t xml:space="preserve">Orange = Postponed</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
+    <t xml:space="preserve">Red = Not useful</t>
   </si>
 </sst>
 </file>
@@ -308,8 +311,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC9211E"/>
-        <bgColor rgb="FF993366"/>
+        <fgColor rgb="FFBF0041"/>
+        <bgColor rgb="FF800080"/>
       </patternFill>
     </fill>
     <fill>
@@ -353,7 +356,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -386,6 +389,14 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -395,6 +406,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -421,7 +436,7 @@
       <rgbColor rgb="FF008000"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FFBF0041"/>
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFC0C0C0"/>
       <rgbColor rgb="FF808080"/>
@@ -461,7 +476,7 @@
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FFC9211E"/>
+      <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
@@ -581,16 +596,16 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N34"/>
+  <dimension ref="A1:L37"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="7.49"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="19.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="10.91"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="11.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="9.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="34.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="11.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="9.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="34.25"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -612,10 +627,10 @@
       <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="2" t="s">
@@ -624,22 +639,16 @@
       <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>11</v>
-      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D2" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -649,41 +658,33 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="F2" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="G2" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="F2" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
       <c r="H2" s="6" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="I2" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="J2" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K2" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="L2" s="2"/>
+      <c r="I2" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>2024</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D3" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -693,41 +694,33 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="F3" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
+      <c r="F3" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
       </c>
       <c r="G3" s="6" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="H3" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="H3" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
       <c r="I3" s="6" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="J3" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="K3" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="L3" s="2"/>
+      <c r="J3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>2024</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D4" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -737,41 +730,33 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="F4" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="F4" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
       <c r="H4" s="6" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="I4" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="J4" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K4" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="L4" s="2"/>
+      <c r="I4" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>2024</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D5" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -781,43 +766,35 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="F5" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="G5" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="F5" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
       <c r="H5" s="6" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="I5" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="J5" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K5" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>20</v>
+      <c r="I5" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>2024</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D6" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -827,41 +804,33 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="F6" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="G6" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="F6" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
       <c r="H6" s="6" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="I6" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="J6" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K6" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="L6" s="2"/>
+      <c r="I6" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>2024</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D7" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -871,43 +840,35 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="F7" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="G7" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="F7" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
       <c r="H7" s="6" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="I7" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="J7" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K7" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>25</v>
+      <c r="I7" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>2024</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D8" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -917,41 +878,33 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="F8" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="G8" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="F8" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
       <c r="H8" s="6" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="I8" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="J8" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="L8" s="2"/>
+      <c r="I8" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>2024</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>29</v>
+      <c r="C9" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="D9" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -961,9 +914,9 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="F9" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
+      <c r="F9" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
       </c>
       <c r="G9" s="6" t="n">
         <f aca="false">FALSE()</f>
@@ -973,29 +926,21 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="I9" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J9" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="L9" s="2"/>
+      <c r="I9" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="J9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>2024</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D10" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1005,41 +950,33 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="F10" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="G10" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="F10" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
       <c r="H10" s="6" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="I10" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="J10" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K10" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="L10" s="2"/>
+      <c r="I10" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>2024</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D11" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1049,9 +986,9 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="F11" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
+      <c r="F11" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
       </c>
       <c r="G11" s="6" t="n">
         <f aca="false">FALSE()</f>
@@ -1061,29 +998,21 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="I11" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J11" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K11" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="L11" s="2"/>
+      <c r="I11" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="J11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>2024</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D12" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1093,9 +1022,9 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="F12" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
+      <c r="F12" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
       </c>
       <c r="G12" s="6" t="n">
         <f aca="false">FALSE()</f>
@@ -1105,29 +1034,21 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="I12" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J12" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K12" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="L12" s="2"/>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
-        <v>34</v>
+      <c r="I12" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="J12" s="2"/>
+    </row>
+    <row r="13" customFormat="false" ht="13.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="8" t="s">
+        <v>32</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>35</v>
+      <c r="C13" s="4" t="s">
+        <v>33</v>
       </c>
       <c r="D13" s="6" t="n">
         <f aca="false">FALSE()</f>
@@ -1141,27 +1062,19 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="G13" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
+      <c r="G13" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
       </c>
       <c r="H13" s="6" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="I13" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J13" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K13" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="L13" s="2"/>
+      <c r="I13" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="J13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
@@ -1170,8 +1083,8 @@
       <c r="B14" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>36</v>
+      <c r="C14" s="4" t="s">
+        <v>35</v>
       </c>
       <c r="D14" s="6" t="n">
         <f aca="false">FALSE()</f>
@@ -1185,83 +1098,67 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="G14" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
+      <c r="G14" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
       </c>
       <c r="H14" s="6" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="I14" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J14" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K14" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="L14" s="2"/>
+      <c r="I14" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="J14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>2025</v>
       </c>
       <c r="C15" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J15" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="D15" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="F15" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="G15" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="H15" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="I15" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="J15" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K15" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>2025</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D16" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1271,41 +1168,33 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="F16" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="G16" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="F16" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
       <c r="H16" s="6" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="I16" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="J16" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K16" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="L16" s="2"/>
+      <c r="I16" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>2025</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D17" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1315,87 +1204,71 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="F17" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="G17" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="F17" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
       <c r="H17" s="6" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="I17" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="J17" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K17" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="L17" s="2"/>
+      <c r="I17" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>2025</v>
       </c>
       <c r="C18" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="D18" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="E18" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="F18" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="G18" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="H18" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="I18" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="J18" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K18" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>48</v>
+      <c r="C19" s="4" t="s">
+        <v>47</v>
       </c>
       <c r="D19" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1405,9 +1278,9 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="F19" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
+      <c r="F19" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
       </c>
       <c r="G19" s="6" t="n">
         <f aca="false">FALSE()</f>
@@ -1417,75 +1290,59 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="I19" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J19" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K19" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="L19" s="2"/>
+      <c r="I19" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="J19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>2025</v>
       </c>
       <c r="C20" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J20" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="D20" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="E20" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="F20" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="G20" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="H20" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="I20" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="J20" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K20" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>53</v>
+      <c r="C21" s="7" t="s">
+        <v>52</v>
       </c>
       <c r="D21" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1495,9 +1352,9 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="F21" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
+      <c r="F21" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
       </c>
       <c r="G21" s="6" t="n">
         <f aca="false">FALSE()</f>
@@ -1507,75 +1364,59 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="I21" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J21" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K21" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="L21" s="2"/>
+      <c r="I21" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="J21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>2025</v>
       </c>
       <c r="C22" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J22" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="D22" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="E22" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="F22" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="G22" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="H22" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="I22" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="J22" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K22" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="L22" s="2" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>58</v>
+      <c r="C23" s="4" t="s">
+        <v>57</v>
       </c>
       <c r="D23" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1585,9 +1426,9 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="F23" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
+      <c r="F23" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
       </c>
       <c r="G23" s="6" t="n">
         <f aca="false">FALSE()</f>
@@ -1597,29 +1438,21 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="I23" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="J23" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K23" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="L23" s="2"/>
+      <c r="I23" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="J23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>2025</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D24" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1629,41 +1462,33 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="F24" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="G24" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="F24" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
       <c r="H24" s="6" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="I24" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="J24" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K24" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="L24" s="2"/>
+      <c r="I24" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>62</v>
+      <c r="C25" s="4" t="s">
+        <v>61</v>
       </c>
       <c r="D25" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1673,41 +1498,33 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="F25" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="G25" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="F25" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
       <c r="H25" s="6" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="I25" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="J25" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K25" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="L25" s="2"/>
+      <c r="I25" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>63</v>
+      <c r="C26" s="4" t="s">
+        <v>62</v>
       </c>
       <c r="D26" s="5" t="n">
         <f aca="false">TRUE()</f>
@@ -1717,75 +1534,61 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="F26" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="G26" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="F26" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
       <c r="H26" s="6" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="I26" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="J26" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K26" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="L26" s="2"/>
+      <c r="I26" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J26" s="2"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="I27" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J27" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D27" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="E27" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="F27" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="G27" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="H27" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="I27" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="J27" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K27" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="L27" s="2"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
@@ -1794,7 +1597,7 @@
       <c r="B28" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="4" t="s">
         <v>66</v>
       </c>
       <c r="D28" s="5" t="n">
@@ -1805,31 +1608,23 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="F28" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="G28" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="F28" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
       <c r="H28" s="6" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="I28" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="J28" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K28" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="L28" s="2"/>
+      <c r="I28" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J28" s="2"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
@@ -1838,7 +1633,7 @@
       <c r="B29" s="2" t="n">
         <v>2026</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="4" t="s">
         <v>68</v>
       </c>
       <c r="D29" s="5" t="n">
@@ -1849,31 +1644,23 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="F29" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="G29" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="F29" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
       <c r="H29" s="6" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="I29" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="J29" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="K29" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="L29" s="2"/>
+      <c r="I29" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="J29" s="2"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
@@ -1893,97 +1680,92 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="F30" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
+      <c r="F30" s="6" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
       </c>
       <c r="G30" s="6" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="H30" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="H30" s="5" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
       </c>
       <c r="I30" s="6" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="J30" s="5" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="K30" s="6" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-      <c r="L30" s="2"/>
+      <c r="J30" s="2"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="8"/>
-      <c r="I31" s="8"/>
-      <c r="J31" s="8"/>
-      <c r="K31" s="8"/>
-      <c r="L31" s="8"/>
-      <c r="M31" s="8"/>
-      <c r="N31" s="8"/>
+      <c r="B31" s="10"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10"/>
+      <c r="F31" s="10"/>
+      <c r="G31" s="10"/>
+      <c r="H31" s="10"/>
+      <c r="I31" s="10"/>
+      <c r="J31" s="10"/>
+      <c r="K31" s="10"/>
+      <c r="L31" s="10"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="8"/>
-      <c r="C32" s="9" t="s">
+      <c r="B32" s="10"/>
+      <c r="C32" s="0"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="10"/>
+      <c r="G32" s="10"/>
+      <c r="H32" s="10"/>
+      <c r="I32" s="10"/>
+      <c r="J32" s="10"/>
+      <c r="K32" s="10"/>
+      <c r="L32" s="10"/>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="10"/>
+      <c r="C33" s="0"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
+      <c r="G33" s="10"/>
+      <c r="H33" s="10"/>
+      <c r="I33" s="10"/>
+      <c r="J33" s="10"/>
+      <c r="K33" s="10"/>
+      <c r="L33" s="10"/>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="8"/>
-      <c r="H32" s="8"/>
-      <c r="I32" s="8"/>
-      <c r="J32" s="8"/>
-      <c r="K32" s="8"/>
-      <c r="L32" s="8"/>
-      <c r="M32" s="8"/>
-      <c r="N32" s="8"/>
-    </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="8"/>
-      <c r="C33" s="10" t="s">
+      <c r="C34" s="0"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="10"/>
+      <c r="F34" s="10"/>
+      <c r="G34" s="10"/>
+      <c r="H34" s="10"/>
+      <c r="I34" s="10"/>
+      <c r="J34" s="10"/>
+      <c r="K34" s="10"/>
+      <c r="L34" s="10"/>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C35" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
-      <c r="G33" s="8"/>
-      <c r="H33" s="8"/>
-      <c r="I33" s="8"/>
-      <c r="J33" s="8"/>
-      <c r="K33" s="8"/>
-      <c r="L33" s="8"/>
-      <c r="M33" s="8"/>
-      <c r="N33" s="8"/>
-    </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="8" t="s">
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C36" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="8"/>
-      <c r="H34" s="8"/>
-      <c r="I34" s="8"/>
-      <c r="J34" s="8"/>
-      <c r="K34" s="8"/>
-      <c r="L34" s="8"/>
-      <c r="M34" s="8"/>
-      <c r="N34" s="8"/>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C37" s="13" t="s">
+        <v>74</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
